--- a/results/Q.xlsx
+++ b/results/Q.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JupyterProjects\sect修订中2\result\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JupyterProjects\sect修订中2\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B7B44C-25FE-4B8D-AEDE-E1AEFD90DF33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF7B69A8-6A3D-49D6-9E32-D21C3823C3DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="210" yWindow="560" windowWidth="18990" windowHeight="10240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="17">
   <si>
     <t>tree</t>
   </si>
@@ -82,6 +82,10 @@
   </si>
   <si>
     <t>Similarity Graph</t>
+  </si>
+  <si>
+    <t>LFR_base</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -476,7 +480,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -499,10 +503,10 @@
         <v>0.71509999999999996</v>
       </c>
       <c r="D2" s="1">
-        <v>0.66500000000000004</v>
+        <v>0.86584700000000003</v>
       </c>
       <c r="E2" s="1">
-        <v>0.88819999999999999</v>
+        <v>0.82695700000000005</v>
       </c>
       <c r="F2" s="1">
         <v>0.94610000000000005</v>
@@ -522,10 +526,10 @@
         <v>0.67325599999999997</v>
       </c>
       <c r="D3" s="2">
-        <v>0.42304799999999998</v>
+        <v>0.77009300000000003</v>
       </c>
       <c r="E3" s="2">
-        <v>0.43151099999999998</v>
+        <v>0.41345199999999999</v>
       </c>
       <c r="F3" s="2">
         <v>0.82062900000000005</v>
@@ -545,10 +549,10 @@
         <v>0.27034599999999998</v>
       </c>
       <c r="D4" s="2">
-        <v>-0.15648300000000001</v>
+        <v>-1.4775999999999999E-2</v>
       </c>
       <c r="E4" s="2">
-        <v>3.8006999999999999E-2</v>
+        <v>2.4120000000000001E-3</v>
       </c>
       <c r="F4" s="2">
         <v>0.13952500000000001</v>
@@ -568,10 +572,10 @@
         <v>0.67325599999999997</v>
       </c>
       <c r="D5" s="2">
-        <v>0.42304799999999998</v>
+        <v>0.77134800000000003</v>
       </c>
       <c r="E5" s="2">
-        <v>0.43176700000000001</v>
+        <v>0.417379</v>
       </c>
       <c r="F5" s="2">
         <v>0.820658</v>
@@ -591,10 +595,10 @@
         <v>0.64460300000000004</v>
       </c>
       <c r="D6" s="2">
-        <v>0.30514599999999997</v>
+        <v>0.72317200000000004</v>
       </c>
       <c r="E6" s="2">
-        <v>-3.4126999999999998E-2</v>
+        <v>7.9135999999999998E-2</v>
       </c>
       <c r="F6" s="2">
         <v>0.813226</v>
@@ -614,10 +618,10 @@
         <v>0.65783100000000005</v>
       </c>
       <c r="D7" s="2">
-        <v>0.37926700000000002</v>
+        <v>0.757378</v>
       </c>
       <c r="E7" s="2">
-        <v>0.36658499999999999</v>
+        <v>0.34713300000000002</v>
       </c>
       <c r="F7" s="2">
         <v>0.78762299999999996</v>
@@ -637,10 +641,10 @@
         <v>0.65783100000000005</v>
       </c>
       <c r="D8" s="2">
-        <v>0.30365399999999998</v>
+        <v>0.77134800000000003</v>
       </c>
       <c r="E8" s="2">
-        <v>0.39022699999999999</v>
+        <v>0.35547200000000001</v>
       </c>
       <c r="F8" s="2">
         <v>0.81613599999999997</v>
@@ -683,10 +687,10 @@
         <v>0.590781</v>
       </c>
       <c r="D11" s="2">
-        <v>0.30470000000000003</v>
+        <v>0.76812800000000003</v>
       </c>
       <c r="E11" s="2">
-        <v>0.37319999999999998</v>
+        <v>0.34740900000000002</v>
       </c>
       <c r="F11" s="2">
         <v>0.73589099999999996</v>
@@ -706,10 +710,10 @@
         <v>0.71508899999999997</v>
       </c>
       <c r="D12" s="2">
-        <v>0.68500000000000005</v>
+        <v>0.86584700000000003</v>
       </c>
       <c r="E12" s="2">
-        <v>0.88824800000000004</v>
+        <v>0.82695700000000005</v>
       </c>
       <c r="F12" s="4">
         <v>0.94613899999999995</v>
